--- a/onskeliste.xlsx
+++ b/onskeliste.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eker-my.sharepoint.com/personal/sondre_eker_no/Documents/Dokumenter/Privat/Bryllup/Nettside/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_EFF37D6E1118E0FA3BAF1A8E0BCA469132152A9A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCCDDCF8-67D1-456D-9DCF-2B0DC916EDBE}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="11_EFF37D6E1118E0FA3BAF1A8E0BCA469132152A9A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82145D23-83D2-4B69-B65C-AAB943A2704A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Ønske</t>
   </si>
@@ -61,16 +61,13 @@
     <t>Alle ønsker vises i samme rekkefølge som i arket.</t>
   </si>
   <si>
-    <t>Vase</t>
-  </si>
-  <si>
-    <t>gjennomsiktig</t>
-  </si>
-  <si>
-    <t>kitchen</t>
-  </si>
-  <si>
-    <t>Spiegelau vinglass</t>
+    <t>Gavekort på opplevelse</t>
+  </si>
+  <si>
+    <t>Penger øremerket til kunst</t>
+  </si>
+  <si>
+    <t>Noe av det fineste vi vet er å oppleve noe sammen. En konsert, teater, en overnatting. Gjerne også sammens med dere</t>
   </si>
 </sst>
 </file>
@@ -391,27 +388,19 @@
         <v>13</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="4">
-        <v>1</v>
-      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="4"/>
       <c r="F2" s="1"/>
     </row>
     <row r="3" spans="1:6" ht="25.05" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B3" s="3"/>
-      <c r="C3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="4">
-        <v>6</v>
-      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="4"/>
       <c r="F3" s="1" t="s">
         <v>5</v>
       </c>
